--- a/balance_sheet.xlsx
+++ b/balance_sheet.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adero\Desktop\finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adero\Desktop\test folder\excel work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{996FD4DB-27FF-4BC1-948C-DF43CC7F3D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354C0A81-4651-4187-8B4D-BFD8EBBF9842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{557D5D03-6CD2-46AE-835E-55A9E3555F89}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{557D5D03-6CD2-46AE-835E-55A9E3555F89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,6 +34,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,12 +513,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3334,13 +3356,13 @@
       </c>
     </row>
     <row r="75" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A77" s="26" t="s">
@@ -5795,12 +5817,12 @@
       </c>
     </row>
     <row r="150" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="29" t="s">
+      <c r="A150" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B150" s="29"/>
-      <c r="C150" s="29"/>
-      <c r="D150" s="29"/>
+      <c r="B150" s="28"/>
+      <c r="C150" s="28"/>
+      <c r="D150" s="28"/>
     </row>
     <row r="153" spans="1:26" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
@@ -6560,13 +6582,13 @@
       </c>
     </row>
     <row r="174" spans="1:26" ht="18" x14ac:dyDescent="0.35">
-      <c r="A174" s="30" t="s">
+      <c r="A174" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B174" s="30"/>
-      <c r="C174" s="30"/>
-      <c r="D174" s="30"/>
-      <c r="E174" s="30"/>
+      <c r="B174" s="29"/>
+      <c r="C174" s="29"/>
+      <c r="D174" s="29"/>
+      <c r="E174" s="29"/>
       <c r="S174" t="s">
         <v>61</v>
       </c>
@@ -9845,12 +9867,12 @@
     </row>
     <row r="282" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="284" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A284" s="28" t="s">
+      <c r="A284" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B284" s="28"/>
-      <c r="C284" s="28"/>
-      <c r="D284" s="28"/>
+      <c r="B284" s="30"/>
+      <c r="C284" s="30"/>
+      <c r="D284" s="30"/>
     </row>
     <row r="285" spans="1:26" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A285" s="26" t="s">
@@ -13874,39 +13896,18 @@
     <row r="413" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A390:C390"/>
-    <mergeCell ref="J390:K390"/>
-    <mergeCell ref="S390:W391"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A362:C362"/>
-    <mergeCell ref="J362:K362"/>
-    <mergeCell ref="S362:W363"/>
-    <mergeCell ref="A388:C388"/>
-    <mergeCell ref="S101:W102"/>
-    <mergeCell ref="S127:W128"/>
-    <mergeCell ref="A77:E78"/>
-    <mergeCell ref="J77:N78"/>
-    <mergeCell ref="S77:W78"/>
-    <mergeCell ref="A50:E51"/>
-    <mergeCell ref="J50:N51"/>
-    <mergeCell ref="S52:W53"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="J1:N2"/>
-    <mergeCell ref="S1:W2"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A27:E28"/>
-    <mergeCell ref="J27:N28"/>
-    <mergeCell ref="S27:W28"/>
-    <mergeCell ref="J180:K180"/>
-    <mergeCell ref="S180:W181"/>
-    <mergeCell ref="A205:E205"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A150:D150"/>
-    <mergeCell ref="S153:W154"/>
-    <mergeCell ref="A174:E174"/>
-    <mergeCell ref="J153:K153"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="J311:K311"/>
+    <mergeCell ref="S311:W312"/>
+    <mergeCell ref="A335:E335"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="J337:K337"/>
+    <mergeCell ref="S337:W338"/>
+    <mergeCell ref="A285:C285"/>
+    <mergeCell ref="J285:K285"/>
+    <mergeCell ref="S285:W286"/>
+    <mergeCell ref="A284:D284"/>
+    <mergeCell ref="A310:C310"/>
     <mergeCell ref="A259:D259"/>
     <mergeCell ref="A260:C260"/>
     <mergeCell ref="J259:K259"/>
@@ -13918,20 +13919,292 @@
     <mergeCell ref="A234:C234"/>
     <mergeCell ref="J234:K234"/>
     <mergeCell ref="S234:W235"/>
-    <mergeCell ref="A285:C285"/>
-    <mergeCell ref="J285:K285"/>
-    <mergeCell ref="S285:W286"/>
-    <mergeCell ref="A284:D284"/>
-    <mergeCell ref="A310:C310"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="J311:K311"/>
-    <mergeCell ref="S311:W312"/>
-    <mergeCell ref="A335:E335"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="J337:K337"/>
-    <mergeCell ref="S337:W338"/>
+    <mergeCell ref="J180:K180"/>
+    <mergeCell ref="S180:W181"/>
+    <mergeCell ref="A205:E205"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="S153:W154"/>
+    <mergeCell ref="A174:E174"/>
+    <mergeCell ref="J153:K153"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="J1:N2"/>
+    <mergeCell ref="S1:W2"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:E28"/>
+    <mergeCell ref="J27:N28"/>
+    <mergeCell ref="S27:W28"/>
+    <mergeCell ref="A50:E51"/>
+    <mergeCell ref="J50:N51"/>
+    <mergeCell ref="S52:W53"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="S101:W102"/>
+    <mergeCell ref="S127:W128"/>
+    <mergeCell ref="A77:E78"/>
+    <mergeCell ref="J77:N78"/>
+    <mergeCell ref="S77:W78"/>
+    <mergeCell ref="A390:C390"/>
+    <mergeCell ref="J390:K390"/>
+    <mergeCell ref="S390:W391"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A362:C362"/>
+    <mergeCell ref="J362:K362"/>
+    <mergeCell ref="S362:W363"/>
+    <mergeCell ref="A388:C388"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341592C0-78BA-4F6D-B7B0-524CF402E55C}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" cm="1">
+        <f t="array" ref="A1:B30">_xlfn.SEQUENCE(30,2)</f>
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>41</v>
+      </c>
+      <c r="B21">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>45</v>
+      </c>
+      <c r="B23">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>49</v>
+      </c>
+      <c r="B25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>51</v>
+      </c>
+      <c r="B26">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>53</v>
+      </c>
+      <c r="B27">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>57</v>
+      </c>
+      <c r="B29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>